--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД.xlsx
@@ -7,15 +7,201 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
+    <sheet name="ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДС" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="59">
+  <si>
+    <t>Дата</t>
+  </si>
+  <si>
+    <t>Станция</t>
+  </si>
+  <si>
+    <t>Име</t>
+  </si>
+  <si>
+    <t>Номер на карта</t>
+  </si>
+  <si>
+    <t>Име на артикул</t>
+  </si>
+  <si>
+    <t>Литри</t>
+  </si>
+  <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
+    <t>GTA цена</t>
+  </si>
+  <si>
+    <t>Сума по GTA цена</t>
+  </si>
+  <si>
+    <t>ЕКО цена</t>
+  </si>
+  <si>
+    <t>Сума по ЕКО цена</t>
+  </si>
+  <si>
+    <t>Час</t>
+  </si>
+  <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>2026-05-14</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-23</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>В3931НА</t>
+  </si>
+  <si>
+    <t>В0922ТК</t>
+  </si>
+  <si>
+    <t>В3164НА</t>
+  </si>
+  <si>
+    <t>78970151027720021</t>
+  </si>
+  <si>
+    <t>78970151027720054</t>
+  </si>
+  <si>
+    <t>78970151027720039</t>
+  </si>
+  <si>
+    <t>DIESEL EKONOMY</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>07:20:00</t>
+  </si>
+  <si>
+    <t>16:30:00</t>
+  </si>
+  <si>
+    <t>07:23:00</t>
+  </si>
+  <si>
+    <t>16:18:00</t>
+  </si>
+  <si>
+    <t>16:44:00</t>
+  </si>
+  <si>
+    <t>16:46:00</t>
+  </si>
+  <si>
+    <t>16:45:00</t>
+  </si>
+  <si>
+    <t>17:10:00</t>
+  </si>
+  <si>
+    <t>09:10:00</t>
+  </si>
+  <si>
+    <t>16:48:00</t>
+  </si>
+  <si>
+    <t>3231404418 3231404418</t>
+  </si>
+  <si>
+    <t>3231412280 3231412280</t>
+  </si>
+  <si>
+    <t>3231696729 3231696729</t>
+  </si>
+  <si>
+    <t>3231748454 3231748454</t>
+  </si>
+  <si>
+    <t>3231734533 3231734533</t>
+  </si>
+  <si>
+    <t>3231880033 3231880033</t>
+  </si>
+  <si>
+    <t>3232047623 3232047623</t>
+  </si>
+  <si>
+    <t>3232045088 3232045088</t>
+  </si>
+  <si>
+    <t>3232202644 3232202644</t>
+  </si>
+  <si>
+    <t>3232288222 3232288222</t>
+  </si>
+  <si>
+    <t>3232435065 3232435065</t>
+  </si>
+  <si>
+    <t>Общи литри по продукт / ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД</t>
+  </si>
+  <si>
+    <t>Продукт</t>
+  </si>
+  <si>
+    <t>Общо / литри</t>
+  </si>
+  <si>
+    <t>Брой транзакции</t>
+  </si>
+  <si>
+    <t>Средна претеглена GTA цена</t>
+  </si>
+  <si>
+    <t>Общо</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -23,16 +209,56 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -40,12 +266,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -340,9 +596,625 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="35.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="8" max="8" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2">
+        <v>27.74</v>
+      </c>
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2">
+        <v>1.67</v>
+      </c>
+      <c r="I2" s="1">
+        <v>46.33</v>
+      </c>
+      <c r="J2">
+        <v>1.8</v>
+      </c>
+      <c r="K2" s="1">
+        <v>49.93</v>
+      </c>
+      <c r="L2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3">
+        <v>49.16</v>
+      </c>
+      <c r="G3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3">
+        <v>1.67</v>
+      </c>
+      <c r="I3" s="1">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="J3">
+        <v>1.8</v>
+      </c>
+      <c r="K3" s="1">
+        <v>88.48999999999999</v>
+      </c>
+      <c r="L3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4">
+        <v>23.24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4">
+        <v>1.66</v>
+      </c>
+      <c r="I4" s="1">
+        <v>38.58</v>
+      </c>
+      <c r="J4">
+        <v>1.79</v>
+      </c>
+      <c r="K4" s="1">
+        <v>41.6</v>
+      </c>
+      <c r="L4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5">
+        <v>44.72</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5">
+        <v>1.66</v>
+      </c>
+      <c r="I5" s="1">
+        <v>74.23999999999999</v>
+      </c>
+      <c r="J5">
+        <v>1.79</v>
+      </c>
+      <c r="K5" s="1">
+        <v>80.05</v>
+      </c>
+      <c r="L5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5">
+        <v>432523</v>
+      </c>
+      <c r="N5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6">
+        <v>54.98</v>
+      </c>
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6">
+        <v>1.66</v>
+      </c>
+      <c r="I6" s="1">
+        <v>91.27</v>
+      </c>
+      <c r="J6">
+        <v>1.79</v>
+      </c>
+      <c r="K6" s="1">
+        <v>98.41</v>
+      </c>
+      <c r="L6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M6">
+        <v>322195</v>
+      </c>
+      <c r="N6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>28.25</v>
+      </c>
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7">
+        <v>1.66</v>
+      </c>
+      <c r="I7" s="1">
+        <v>46.9</v>
+      </c>
+      <c r="J7">
+        <v>1.77</v>
+      </c>
+      <c r="K7" s="1">
+        <v>50</v>
+      </c>
+      <c r="L7" t="s">
+        <v>37</v>
+      </c>
+      <c r="M7">
+        <v>322575</v>
+      </c>
+      <c r="N7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8">
+        <v>22.8</v>
+      </c>
+      <c r="G8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8">
+        <v>1.65</v>
+      </c>
+      <c r="I8" s="1">
+        <v>37.62</v>
+      </c>
+      <c r="J8">
+        <v>1.75</v>
+      </c>
+      <c r="K8" s="1">
+        <v>39.9</v>
+      </c>
+      <c r="L8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9">
+        <v>48</v>
+      </c>
+      <c r="G9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9">
+        <v>1.65</v>
+      </c>
+      <c r="I9" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="J9">
+        <v>1.75</v>
+      </c>
+      <c r="K9" s="1">
+        <v>84</v>
+      </c>
+      <c r="L9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M9">
+        <v>322880</v>
+      </c>
+      <c r="N9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10">
+        <v>22.86</v>
+      </c>
+      <c r="G10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10">
+        <v>1.64</v>
+      </c>
+      <c r="I10" s="1">
+        <v>37.49</v>
+      </c>
+      <c r="J10">
+        <v>1.75</v>
+      </c>
+      <c r="K10" s="1">
+        <v>40</v>
+      </c>
+      <c r="L10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M10">
+        <v>323245</v>
+      </c>
+      <c r="N10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11">
+        <v>28.24</v>
+      </c>
+      <c r="G11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11">
+        <v>1.64</v>
+      </c>
+      <c r="I11" s="1">
+        <v>46.31</v>
+      </c>
+      <c r="J11">
+        <v>1.73</v>
+      </c>
+      <c r="K11" s="1">
+        <v>48.86</v>
+      </c>
+      <c r="L11" t="s">
+        <v>40</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12">
+        <v>48.84</v>
+      </c>
+      <c r="G12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12">
+        <v>1.64</v>
+      </c>
+      <c r="I12" s="1">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="J12">
+        <v>1.72</v>
+      </c>
+      <c r="K12" s="1">
+        <v>84</v>
+      </c>
+      <c r="L12" t="s">
+        <v>41</v>
+      </c>
+      <c r="M12">
+        <v>323485</v>
+      </c>
+      <c r="N12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="6">
+        <v>398.83</v>
+      </c>
+      <c r="C17" s="6">
+        <v>11</v>
+      </c>
+      <c r="D17" s="7">
+        <v>1.6552</v>
+      </c>
+      <c r="E17" s="6">
+        <v>660.14</v>
+      </c>
+      <c r="F17" s="6">
+        <v>705.24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="9">
+        <v>398.83</v>
+      </c>
+      <c r="C18" s="9">
+        <v>11</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" s="9">
+        <v>660.14</v>
+      </c>
+      <c r="F18" s="9">
+        <v>705.24</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A15:F15"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД.xlsx
@@ -226,7 +226,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -236,12 +236,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -291,17 +285,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="72">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-01</t>
   </si>
   <si>
@@ -73,76 +82,136 @@
     <t>2026-06-25</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
   </si>
   <si>
     <t>В3931НА</t>
   </si>
   <si>
+    <t>В3164НА</t>
+  </si>
+  <si>
     <t>В0922ТК</t>
   </si>
   <si>
-    <t>В3164НА</t>
-  </si>
-  <si>
     <t>78970151027720021</t>
   </si>
   <si>
+    <t>78970151027720039</t>
+  </si>
+  <si>
     <t>78970151027720054</t>
   </si>
   <si>
-    <t>78970151027720039</t>
-  </si>
-  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
     <t>DIESEL DOUBLE FILTERED</t>
   </si>
   <si>
-    <t>2026-06-01 07:22:08</t>
-  </si>
-  <si>
-    <t>2026-06-01 16:51:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 19:54:28</t>
-  </si>
-  <si>
-    <t>2026-06-01 19:58:12</t>
-  </si>
-  <si>
-    <t>2026-06-04 16:36:02</t>
-  </si>
-  <si>
-    <t>2026-06-09 07:28:28</t>
-  </si>
-  <si>
-    <t>2026-06-10 16:34:10</t>
-  </si>
-  <si>
-    <t>2026-06-10 17:16:33</t>
-  </si>
-  <si>
-    <t>2026-06-15 17:06:45</t>
-  </si>
-  <si>
-    <t>2026-06-18 17:15:15</t>
-  </si>
-  <si>
-    <t>2026-06-22 07:20:58</t>
-  </si>
-  <si>
-    <t>2026-06-22 16:44:27</t>
-  </si>
-  <si>
-    <t>2026-06-25 16:46:04</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>07:22:00</t>
+  </si>
+  <si>
+    <t>19:58:00</t>
+  </si>
+  <si>
+    <t>19:54:00</t>
+  </si>
+  <si>
+    <t>16:50:00</t>
+  </si>
+  <si>
+    <t>16:35:00</t>
+  </si>
+  <si>
+    <t>07:28:00</t>
+  </si>
+  <si>
+    <t>16:34:00</t>
+  </si>
+  <si>
+    <t>17:16:00</t>
+  </si>
+  <si>
+    <t>17:07:00</t>
+  </si>
+  <si>
+    <t>17:15:00</t>
+  </si>
+  <si>
+    <t>07:21:00</t>
+  </si>
+  <si>
+    <t>16:44:00</t>
+  </si>
+  <si>
+    <t>16:45:00</t>
+  </si>
+  <si>
+    <t>14:43:00</t>
+  </si>
+  <si>
+    <t>17:02:00</t>
+  </si>
+  <si>
+    <t>3232708819 3232708819</t>
+  </si>
+  <si>
+    <t>3232724287 3232724287</t>
+  </si>
+  <si>
+    <t>3232724739 3232724739</t>
+  </si>
+  <si>
+    <t>3232724528 3232724528</t>
+  </si>
+  <si>
+    <t>3232864039 3232864039</t>
+  </si>
+  <si>
+    <t>3233067079 3233067079</t>
+  </si>
+  <si>
+    <t>3233124585 3233124585</t>
+  </si>
+  <si>
+    <t>3233151762 3233151762</t>
+  </si>
+  <si>
+    <t>3233399021 3233399021</t>
+  </si>
+  <si>
+    <t>3233539883 3233539883</t>
+  </si>
+  <si>
+    <t>3233715211 3233715211</t>
+  </si>
+  <si>
+    <t>3233727467 3233727467</t>
+  </si>
+  <si>
+    <t>3233867596 3233867596</t>
+  </si>
+  <si>
+    <t>3234008251 3234008251</t>
+  </si>
+  <si>
+    <t>3234065992 3234065992</t>
   </si>
   <si>
     <t>Общи литри по продукт / ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД</t>
@@ -560,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -569,14 +638,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -610,553 +682,767 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>25.52</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2">
         <v>1.62</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>41.34</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.69</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>43.13</v>
       </c>
-      <c r="K2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3">
+        <v>30.48</v>
+      </c>
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3">
+        <v>1.62</v>
+      </c>
+      <c r="I3" s="1">
+        <v>49.38</v>
+      </c>
+      <c r="J3">
+        <v>1.69</v>
+      </c>
+      <c r="K3" s="1">
+        <v>51.51</v>
+      </c>
+      <c r="L3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3">
+        <v>433115</v>
+      </c>
+      <c r="N3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
         <v>28</v>
       </c>
-      <c r="F3">
-        <v>56.74</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.62</v>
-      </c>
-      <c r="H3">
-        <v>91.92</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="J3">
-        <v>95.89</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="D4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F4">
         <v>14.73</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4">
         <v>1.62</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>23.86</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.69</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>24.89</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4">
+        <v>433115</v>
+      </c>
+      <c r="N4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>27</v>
-      </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F5">
-        <v>30.48</v>
-      </c>
-      <c r="G5" s="1">
+        <v>56.74</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5">
         <v>1.62</v>
       </c>
-      <c r="H5">
-        <v>49.38</v>
-      </c>
       <c r="I5" s="1">
+        <v>91.92</v>
+      </c>
+      <c r="J5">
         <v>1.69</v>
       </c>
-      <c r="J5">
-        <v>51.51</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="K5" s="1">
+        <v>95.89</v>
+      </c>
+      <c r="L5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5">
+        <v>323995</v>
+      </c>
+      <c r="N5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
       </c>
       <c r="F6">
         <v>20.48</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6">
         <v>1.59</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>32.56</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.66</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>34</v>
       </c>
-      <c r="K6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6">
+        <v>324340</v>
+      </c>
+      <c r="N6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F7">
         <v>36.27</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7">
         <v>1.56</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>56.58</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.64</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>59.48</v>
       </c>
-      <c r="K7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F8">
         <v>50.01</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8">
         <v>1.88</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>94.02</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.88</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>94.02</v>
       </c>
-      <c r="K8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" t="s">
+        <v>42</v>
+      </c>
+      <c r="M8">
+        <v>324640</v>
+      </c>
+      <c r="N8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F9">
         <v>46.48</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9">
         <v>1.56</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>72.51000000000001</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.63</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>75.76000000000001</v>
       </c>
-      <c r="K9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M9">
+        <v>433713</v>
+      </c>
+      <c r="N9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F10">
         <v>39.09</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10">
         <v>1.56</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>60.98</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.6</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>62.54</v>
       </c>
-      <c r="K10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10" t="s">
+        <v>44</v>
+      </c>
+      <c r="M10">
+        <v>325000</v>
+      </c>
+      <c r="N10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F11">
         <v>25.32</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11">
         <v>1.55</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>39.25</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.58</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>40.01</v>
       </c>
-      <c r="K11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11" t="s">
+        <v>45</v>
+      </c>
+      <c r="M11">
+        <v>325375</v>
+      </c>
+      <c r="N11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F12">
         <v>39.45</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12">
         <v>1.48</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>58.39</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.52</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>59.96</v>
       </c>
-      <c r="K12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12" t="s">
+        <v>46</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F13">
         <v>48.93</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13">
         <v>1.48</v>
       </c>
-      <c r="H13">
+      <c r="I13" s="1">
         <v>72.42</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13">
         <v>1.52</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="1">
         <v>74.37</v>
       </c>
-      <c r="K13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="L13" t="s">
+        <v>47</v>
+      </c>
+      <c r="M13">
+        <v>325675</v>
+      </c>
+      <c r="N13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F14">
         <v>26.5</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14">
         <v>1.47</v>
       </c>
-      <c r="H14">
+      <c r="I14" s="1">
         <v>38.96</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14">
         <v>1.51</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="1">
         <v>40.02</v>
       </c>
-      <c r="K14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>9</v>
+      <c r="L14" t="s">
+        <v>48</v>
+      </c>
+      <c r="M14">
+        <v>326110</v>
+      </c>
+      <c r="N14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15">
+        <v>48.55</v>
+      </c>
+      <c r="G15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15">
+        <v>1.45</v>
+      </c>
+      <c r="I15" s="1">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="J15">
+        <v>1.51</v>
+      </c>
+      <c r="K15" s="1">
+        <v>73.31</v>
+      </c>
+      <c r="L15" t="s">
+        <v>49</v>
+      </c>
+      <c r="M15">
+        <v>434351</v>
+      </c>
+      <c r="N15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16">
+        <v>46.76</v>
+      </c>
+      <c r="G16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16">
+        <v>1.44</v>
+      </c>
+      <c r="I16" s="1">
+        <v>67.33</v>
+      </c>
+      <c r="J16">
+        <v>1.51</v>
+      </c>
+      <c r="K16" s="1">
+        <v>70.61</v>
+      </c>
+      <c r="L16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16">
+        <v>326345</v>
+      </c>
+      <c r="N16" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="6">
-        <v>409.99</v>
-      </c>
-      <c r="C19" s="6">
-        <v>12</v>
-      </c>
-      <c r="D19" s="7">
-        <v>1.5565</v>
-      </c>
-      <c r="E19" s="6">
-        <v>638.15</v>
-      </c>
-      <c r="F19" s="6">
-        <v>661.5599999999999</v>
-      </c>
+      <c r="A19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="6">
+      <c r="A20" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="6">
+        <v>505.3</v>
+      </c>
+      <c r="C21" s="6">
+        <v>14</v>
+      </c>
+      <c r="D21" s="7">
+        <v>1.5355</v>
+      </c>
+      <c r="E21" s="6">
+        <v>775.88</v>
+      </c>
+      <c r="F21" s="6">
+        <v>805.48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="6">
         <v>50.01</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C22" s="6">
         <v>1</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D22" s="7">
         <v>1.88</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E22" s="6">
         <v>94.02</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F22" s="6">
         <v>94.02</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="9">
-        <v>460</v>
-      </c>
-      <c r="C21" s="9">
-        <v>13</v>
-      </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="9">
-        <v>732.17</v>
-      </c>
-      <c r="F21" s="9">
-        <v>755.58</v>
+    <row r="23" spans="1:6">
+      <c r="A23" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="9">
+        <v>555.3099999999999</v>
+      </c>
+      <c r="C23" s="9">
+        <v>15</v>
+      </c>
+      <c r="D23" s="7"/>
+      <c r="E23" s="9">
+        <v>869.9</v>
+      </c>
+      <c r="F23" s="9">
+        <v>899.5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A19:F19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="69">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-02</t>
   </si>
   <si>
@@ -67,13 +73,31 @@
     <t>2026-07-15</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна</t>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
   </si>
   <si>
     <t>В3931НА</t>
@@ -97,28 +121,88 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-07-02 07:24:26</t>
-  </si>
-  <si>
-    <t>2026-07-02 17:29:19</t>
-  </si>
-  <si>
-    <t>2026-07-06 09:27:08</t>
-  </si>
-  <si>
-    <t>2026-07-07 16:27:27</t>
-  </si>
-  <si>
-    <t>2026-07-13 07:25:12</t>
-  </si>
-  <si>
-    <t>2026-07-13 16:18:55</t>
-  </si>
-  <si>
-    <t>2026-07-13 16:44:22</t>
-  </si>
-  <si>
-    <t>2026-07-15 16:27:04</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>07:24:00</t>
+  </si>
+  <si>
+    <t>17:29:00</t>
+  </si>
+  <si>
+    <t>09:27:00</t>
+  </si>
+  <si>
+    <t>16:28:00</t>
+  </si>
+  <si>
+    <t>07:25:00</t>
+  </si>
+  <si>
+    <t>16:18:00</t>
+  </si>
+  <si>
+    <t>16:44:00</t>
+  </si>
+  <si>
+    <t>16:26:00</t>
+  </si>
+  <si>
+    <t>17:05:00</t>
+  </si>
+  <si>
+    <t>07:20:00</t>
+  </si>
+  <si>
+    <t>10:27:00</t>
+  </si>
+  <si>
+    <t>16:19:00</t>
+  </si>
+  <si>
+    <t>17:15:00</t>
+  </si>
+  <si>
+    <t>3234192970 3234192970</t>
+  </si>
+  <si>
+    <t>3234212368 3234212368</t>
+  </si>
+  <si>
+    <t>3234384593 3234384593</t>
+  </si>
+  <si>
+    <t>3234454349 3234454349</t>
+  </si>
+  <si>
+    <t>3234734712 3234734712</t>
+  </si>
+  <si>
+    <t>3234744920 3234744920</t>
+  </si>
+  <si>
+    <t>3234753106 3234753106</t>
+  </si>
+  <si>
+    <t>3234846335 3234846335</t>
+  </si>
+  <si>
+    <t>3235100811 3235100811</t>
+  </si>
+  <si>
+    <t>3235231404 3235231404</t>
+  </si>
+  <si>
+    <t>3235438016 3235438016</t>
+  </si>
+  <si>
+    <t>3235486807 3235486807</t>
+  </si>
+  <si>
+    <t>3235503098 3235503098</t>
+  </si>
+  <si>
+    <t>3235595557 3235595557</t>
   </si>
   <si>
     <t>Общи литри по продукт / ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД</t>
@@ -536,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -545,15 +629,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -590,382 +676,700 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F2">
         <v>54.01</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2">
         <v>1.44</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>77.77</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.51</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>81.56</v>
       </c>
-      <c r="K2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="N2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F3">
         <v>26.49</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3">
         <v>1.44</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>38.15</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.51</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>40</v>
       </c>
-      <c r="K3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3">
+      <c r="L3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3">
         <v>326780</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="N3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F4">
         <v>37.68</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4">
         <v>1.45</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>54.64</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.52</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>57.27</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4">
+        <v>326980</v>
+      </c>
+      <c r="N4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
         <v>29</v>
       </c>
-      <c r="L4">
-        <v>326980</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F5">
         <v>48.16</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5">
         <v>1.45</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>69.83</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.52</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>73.2</v>
       </c>
-      <c r="K5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5">
+      <c r="L5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="N5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F6">
         <v>52.6</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6">
         <v>1.49</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>78.37</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.56</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>82.06</v>
       </c>
-      <c r="K6" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6">
+      <c r="L6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="N6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F7">
         <v>44.83</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7">
         <v>1.49</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>66.8</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.56</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>69.93000000000001</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7">
+        <v>434962</v>
+      </c>
+      <c r="N7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
         <v>32</v>
       </c>
-      <c r="L7">
-        <v>434962</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" t="s">
-        <v>24</v>
-      </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F8">
         <v>51.61</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8">
         <v>1.49</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>76.90000000000001</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.56</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>80.51000000000001</v>
       </c>
-      <c r="K8" t="s">
-        <v>33</v>
-      </c>
-      <c r="L8">
+      <c r="L8" t="s">
+        <v>42</v>
+      </c>
+      <c r="M8">
         <v>327450</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="N8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F9">
         <v>25.35</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9">
         <v>1.53</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>38.79</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.58</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>40.05</v>
       </c>
-      <c r="K9" t="s">
-        <v>34</v>
-      </c>
-      <c r="L9">
+      <c r="L9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M9">
         <v>327760</v>
       </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="3" t="s">
+      <c r="N9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10">
+        <v>42.92</v>
+      </c>
+      <c r="G10" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="5" t="s">
+      <c r="H10">
+        <v>1.59</v>
+      </c>
+      <c r="I10" s="1">
+        <v>68.23999999999999</v>
+      </c>
+      <c r="J10">
+        <v>1.68</v>
+      </c>
+      <c r="K10" s="1">
+        <v>72.11</v>
+      </c>
+      <c r="L10" t="s">
+        <v>44</v>
+      </c>
+      <c r="M10">
+        <v>328090</v>
+      </c>
+      <c r="N10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11">
+        <v>33.71</v>
+      </c>
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11">
+        <v>1.63</v>
+      </c>
+      <c r="I11" s="1">
+        <v>54.95</v>
+      </c>
+      <c r="J11">
+        <v>1.7</v>
+      </c>
+      <c r="K11" s="1">
+        <v>57.31</v>
+      </c>
+      <c r="L11" t="s">
+        <v>45</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="6">
-        <v>340.73</v>
-      </c>
-      <c r="C14" s="6">
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12">
+        <v>49.27</v>
+      </c>
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12">
+        <v>1.66</v>
+      </c>
+      <c r="I12" s="1">
+        <v>81.79000000000001</v>
+      </c>
+      <c r="J12">
+        <v>1.75</v>
+      </c>
+      <c r="K12" s="1">
+        <v>86.22</v>
+      </c>
+      <c r="L12" t="s">
+        <v>46</v>
+      </c>
+      <c r="M12">
+        <v>328540</v>
+      </c>
+      <c r="N12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13">
+        <v>47.76</v>
+      </c>
+      <c r="G13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13">
+        <v>1.69</v>
+      </c>
+      <c r="I13" s="1">
+        <v>80.70999999999999</v>
+      </c>
+      <c r="J13">
+        <v>1.75</v>
+      </c>
+      <c r="K13" s="1">
+        <v>83.58</v>
+      </c>
+      <c r="L13" t="s">
+        <v>47</v>
+      </c>
+      <c r="M13">
+        <v>435629</v>
+      </c>
+      <c r="N13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14">
+        <v>54.73</v>
+      </c>
+      <c r="G14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14">
+        <v>1.71</v>
+      </c>
+      <c r="I14" s="1">
+        <v>93.59</v>
+      </c>
+      <c r="J14">
+        <v>1.75</v>
+      </c>
+      <c r="K14" s="1">
+        <v>95.78</v>
+      </c>
+      <c r="L14" t="s">
+        <v>45</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15">
+        <v>34.1</v>
+      </c>
+      <c r="G15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15">
+        <v>1.71</v>
+      </c>
+      <c r="I15" s="1">
+        <v>58.31</v>
+      </c>
+      <c r="J15">
+        <v>1.76</v>
+      </c>
+      <c r="K15" s="1">
+        <v>60.02</v>
+      </c>
+      <c r="L15" t="s">
+        <v>48</v>
+      </c>
+      <c r="M15">
+        <v>328945</v>
+      </c>
+      <c r="N15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="7">
-        <v>1.4711</v>
-      </c>
-      <c r="E14" s="6">
-        <v>501.25</v>
-      </c>
-      <c r="F14" s="6">
-        <v>524.58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="9">
-        <v>340.73</v>
-      </c>
-      <c r="C15" s="9">
-        <v>8</v>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="9">
-        <v>501.25</v>
-      </c>
-      <c r="F15" s="9">
-        <v>524.58</v>
+      <c r="F19" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="6">
+        <v>603.22</v>
+      </c>
+      <c r="C20" s="6">
+        <v>14</v>
+      </c>
+      <c r="D20" s="7">
+        <v>1.5564</v>
+      </c>
+      <c r="E20" s="6">
+        <v>938.84</v>
+      </c>
+      <c r="F20" s="6">
+        <v>979.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="9">
+        <v>603.22</v>
+      </c>
+      <c r="C21" s="9">
+        <v>14</v>
+      </c>
+      <c r="D21" s="7"/>
+      <c r="E21" s="9">
+        <v>938.84</v>
+      </c>
+      <c r="F21" s="9">
+        <v>979.6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД.xlsx
@@ -229,7 +229,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1340,7 +1340,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="7">
-        <v>1.5564</v>
+        <v>1.556381</v>
       </c>
       <c r="E20" s="6">
         <v>938.84</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\SPLIT_COMPANY_DATA\RESULT\companies_result\ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1DCF922-9C9E-4EFE-9C1B-60D86ADCFEC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДС" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="74">
   <si>
     <t>Дата</t>
   </si>
@@ -76,6 +82,9 @@
     <t>2026-07-20</t>
   </si>
   <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
     <t>2026-07-23</t>
   </si>
   <si>
@@ -109,6 +118,9 @@
     <t>В3164НА</t>
   </si>
   <si>
+    <t>В4286ХМ</t>
+  </si>
+  <si>
     <t>78970151027720021</t>
   </si>
   <si>
@@ -118,6 +130,9 @@
     <t>78970151027720039</t>
   </si>
   <si>
+    <t>78970151027721052</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
@@ -151,6 +166,9 @@
     <t>17:05:00</t>
   </si>
   <si>
+    <t>16:30:00</t>
+  </si>
+  <si>
     <t>07:20:00</t>
   </si>
   <si>
@@ -188,6 +206,9 @@
   </si>
   <si>
     <t>3235100811 3235100811</t>
+  </si>
+  <si>
+    <t>3235153889 3235153889</t>
   </si>
   <si>
     <t>3235231404 3235231404</t>
@@ -226,12 +247,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.000000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -256,7 +276,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -278,6 +298,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -309,36 +335,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -376,7 +412,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -410,6 +446,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -444,9 +481,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -619,9 +657,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
@@ -639,7 +677,7 @@
     <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -683,27 +721,27 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F2">
         <v>54.01</v>
       </c>
       <c r="G2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H2">
         <v>1.44</v>
@@ -718,36 +756,36 @@
         <v>81.56</v>
       </c>
       <c r="L2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F3">
         <v>26.49</v>
       </c>
       <c r="G3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H3">
         <v>1.44</v>
@@ -762,36 +800,36 @@
         <v>40</v>
       </c>
       <c r="L3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M3">
         <v>326780</v>
       </c>
       <c r="N3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F4">
         <v>37.68</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H4">
         <v>1.45</v>
@@ -806,36 +844,36 @@
         <v>57.27</v>
       </c>
       <c r="L4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M4">
         <v>326980</v>
       </c>
       <c r="N4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F5">
         <v>48.16</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H5">
         <v>1.45</v>
@@ -850,36 +888,36 @@
         <v>73.2</v>
       </c>
       <c r="L5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F6">
         <v>52.6</v>
       </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H6">
         <v>1.49</v>
@@ -894,36 +932,36 @@
         <v>82.06</v>
       </c>
       <c r="L6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F7">
         <v>44.83</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H7">
         <v>1.49</v>
@@ -935,83 +973,83 @@
         <v>1.56</v>
       </c>
       <c r="K7" s="1">
-        <v>69.93000000000001</v>
+        <v>69.930000000000007</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M7">
         <v>434962</v>
       </c>
       <c r="N7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F8">
         <v>51.61</v>
       </c>
       <c r="G8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H8">
         <v>1.49</v>
       </c>
       <c r="I8" s="1">
-        <v>76.90000000000001</v>
+        <v>76.900000000000006</v>
       </c>
       <c r="J8">
         <v>1.56</v>
       </c>
       <c r="K8" s="1">
-        <v>80.51000000000001</v>
+        <v>80.510000000000005</v>
       </c>
       <c r="L8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M8">
         <v>327450</v>
       </c>
       <c r="N8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F9">
         <v>25.35</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H9">
         <v>1.53</v>
@@ -1023,45 +1061,45 @@
         <v>1.58</v>
       </c>
       <c r="K9" s="1">
-        <v>40.05</v>
+        <v>40.049999999999997</v>
       </c>
       <c r="L9" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M9">
         <v>327760</v>
       </c>
       <c r="N9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F10">
         <v>42.92</v>
       </c>
       <c r="G10" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H10">
         <v>1.59</v>
       </c>
       <c r="I10" s="1">
-        <v>68.23999999999999</v>
+        <v>68.239999999999995</v>
       </c>
       <c r="J10">
         <v>1.68</v>
@@ -1070,60 +1108,60 @@
         <v>72.11</v>
       </c>
       <c r="L10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M10">
         <v>328090</v>
       </c>
       <c r="N10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B11" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11">
-        <v>33.71</v>
-      </c>
-      <c r="G11" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11">
-        <v>1.63</v>
-      </c>
-      <c r="I11" s="1">
-        <v>54.95</v>
-      </c>
-      <c r="J11">
-        <v>1.7</v>
-      </c>
-      <c r="K11" s="1">
-        <v>57.31</v>
-      </c>
-      <c r="L11" t="s">
-        <v>45</v>
-      </c>
-      <c r="M11">
+      <c r="C11" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="10">
+        <v>54.28</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="I11" s="11">
+        <v>86.85</v>
+      </c>
+      <c r="J11" s="10">
+        <v>1.68</v>
+      </c>
+      <c r="K11" s="11">
+        <v>91.19</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="M11" s="10">
         <v>0</v>
       </c>
-      <c r="N11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="N11" s="10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1134,128 +1172,128 @@
         <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F12">
-        <v>49.27</v>
+        <v>33.71</v>
       </c>
       <c r="G12" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H12">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="I12" s="1">
-        <v>81.79000000000001</v>
+        <v>54.95</v>
       </c>
       <c r="J12">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="K12" s="1">
-        <v>86.22</v>
+        <v>57.31</v>
       </c>
       <c r="L12" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="M12">
-        <v>328540</v>
+        <v>0</v>
       </c>
       <c r="N12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
         <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F13">
-        <v>47.76</v>
+        <v>49.27</v>
       </c>
       <c r="G13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H13">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="I13" s="1">
-        <v>80.70999999999999</v>
+        <v>81.790000000000006</v>
       </c>
       <c r="J13">
         <v>1.75</v>
       </c>
       <c r="K13" s="1">
-        <v>83.58</v>
+        <v>86.22</v>
       </c>
       <c r="L13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M13">
-        <v>435629</v>
+        <v>328540</v>
       </c>
       <c r="N13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F14">
-        <v>54.73</v>
+        <v>47.76</v>
       </c>
       <c r="G14" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H14">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="I14" s="1">
-        <v>93.59</v>
+        <v>80.709999999999994</v>
       </c>
       <c r="J14">
         <v>1.75</v>
       </c>
       <c r="K14" s="1">
-        <v>95.78</v>
+        <v>83.58</v>
       </c>
       <c r="L14" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>435629</v>
       </c>
       <c r="N14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -1266,110 +1304,154 @@
         <v>29</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F15">
-        <v>34.1</v>
+        <v>54.73</v>
       </c>
       <c r="G15" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H15">
         <v>1.71</v>
       </c>
       <c r="I15" s="1">
+        <v>93.59</v>
+      </c>
+      <c r="J15">
+        <v>1.75</v>
+      </c>
+      <c r="K15" s="1">
+        <v>95.78</v>
+      </c>
+      <c r="L15" t="s">
+        <v>49</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16">
+        <v>34.1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H16">
+        <v>1.71</v>
+      </c>
+      <c r="I16" s="1">
         <v>58.31</v>
       </c>
-      <c r="J15">
+      <c r="J16">
         <v>1.76</v>
       </c>
-      <c r="K15" s="1">
+      <c r="K16" s="1">
         <v>60.02</v>
       </c>
-      <c r="L15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M15">
+      <c r="L16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M16">
         <v>328945</v>
       </c>
-      <c r="N15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="N16" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="4" t="s">
+    </row>
+    <row r="19" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A19" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F20" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20" s="6">
-        <v>603.22</v>
-      </c>
-      <c r="C20" s="6">
-        <v>14</v>
-      </c>
-      <c r="D20" s="7">
-        <v>1.556381</v>
-      </c>
-      <c r="E20" s="6">
-        <v>938.84</v>
-      </c>
-      <c r="F20" s="6">
-        <v>979.6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B21" s="9">
-        <v>603.22</v>
-      </c>
-      <c r="C21" s="9">
-        <v>14</v>
-      </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="9">
-        <v>938.84</v>
-      </c>
-      <c r="F21" s="9">
-        <v>979.6</v>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="5">
+        <v>657.5</v>
+      </c>
+      <c r="C21" s="5">
+        <v>15</v>
+      </c>
+      <c r="D21" s="6">
+        <v>1.559985</v>
+      </c>
+      <c r="E21" s="5">
+        <v>1025.69</v>
+      </c>
+      <c r="F21" s="5">
+        <v>1070.79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="8">
+        <v>657.5</v>
+      </c>
+      <c r="C22" s="8">
+        <v>15</v>
+      </c>
+      <c r="D22" s="6"/>
+      <c r="E22" s="8">
+        <v>1025.69</v>
+      </c>
+      <c r="F22" s="8">
+        <v>1070.79</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A19:F19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\SPLIT_COMPANY_DATA\RESULT\companies_result\ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1DCF922-9C9E-4EFE-9C1B-60D86ADCFEC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДС" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="75">
   <si>
     <t>Дата</t>
   </si>
@@ -41,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -247,11 +244,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.000000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,7 +274,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -298,12 +296,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF66"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -335,46 +327,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -412,7 +394,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -446,7 +428,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -481,10 +462,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -657,9 +637,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O22"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
@@ -671,13 +651,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -720,732 +700,780 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2">
-        <v>54.01</v>
+        <v>54.013</v>
       </c>
       <c r="G2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H2">
-        <v>1.44</v>
+        <v>1.399</v>
       </c>
       <c r="I2" s="1">
-        <v>77.77</v>
+        <v>1.439</v>
       </c>
       <c r="J2">
+        <v>77.724707</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.51</v>
       </c>
-      <c r="K2" s="1">
-        <v>81.56</v>
-      </c>
-      <c r="L2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M2">
+      <c r="L2" s="1">
+        <v>81.55963</v>
+      </c>
+      <c r="M2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N2">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F3">
         <v>26.49</v>
       </c>
       <c r="G3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H3">
-        <v>1.44</v>
+        <v>1.399</v>
       </c>
       <c r="I3" s="1">
-        <v>38.15</v>
+        <v>1.439</v>
       </c>
       <c r="J3">
+        <v>38.11911</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.51</v>
       </c>
-      <c r="K3" s="1">
-        <v>40</v>
-      </c>
-      <c r="L3" t="s">
-        <v>40</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>39.9999</v>
+      </c>
+      <c r="M3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3">
         <v>326780</v>
       </c>
-      <c r="N3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4">
+        <v>37.678</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4">
+        <v>1.406</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.446</v>
+      </c>
+      <c r="J4">
+        <v>54.482388</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L4" s="1">
+        <v>57.27056</v>
+      </c>
+      <c r="M4" t="s">
+        <v>42</v>
+      </c>
+      <c r="N4">
+        <v>326980</v>
+      </c>
+      <c r="O4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5">
+        <v>48.158</v>
+      </c>
+      <c r="G5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5">
+        <v>1.406</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.446</v>
+      </c>
+      <c r="J5">
+        <v>69.63646799999999</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L5" s="1">
+        <v>73.20016</v>
+      </c>
+      <c r="M5" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
         <v>30</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D6" t="s">
         <v>34</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6">
+        <v>52.603</v>
+      </c>
+      <c r="G6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6">
+        <v>1.451</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.491</v>
+      </c>
+      <c r="J6">
+        <v>78.431073</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="L6" s="1">
+        <v>82.06068</v>
+      </c>
+      <c r="M6" t="s">
+        <v>44</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>44.827</v>
+      </c>
+      <c r="G7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7">
+        <v>1.451</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.491</v>
+      </c>
+      <c r="J7">
+        <v>66.837057</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="L7" s="1">
+        <v>69.93012</v>
+      </c>
+      <c r="M7" t="s">
+        <v>45</v>
+      </c>
+      <c r="N7">
+        <v>434962</v>
+      </c>
+      <c r="O7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8">
+        <v>51.609</v>
+      </c>
+      <c r="G8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8">
+        <v>1.451</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.491</v>
+      </c>
+      <c r="J8">
+        <v>76.94901900000001</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="L8" s="1">
+        <v>80.51004</v>
+      </c>
+      <c r="M8" t="s">
+        <v>46</v>
+      </c>
+      <c r="N8">
+        <v>327450</v>
+      </c>
+      <c r="O8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9">
+        <v>25.348</v>
+      </c>
+      <c r="G9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9">
+        <v>1.489</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1.529</v>
+      </c>
+      <c r="J9">
+        <v>38.757092</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="L9" s="1">
+        <v>40.04984</v>
+      </c>
+      <c r="M9" t="s">
+        <v>47</v>
+      </c>
+      <c r="N9">
+        <v>327760</v>
+      </c>
+      <c r="O9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10">
+        <v>42.923</v>
+      </c>
+      <c r="G10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10">
+        <v>1.546</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1.586</v>
+      </c>
+      <c r="J10">
+        <v>68.075878</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="L10" s="1">
+        <v>72.11064</v>
+      </c>
+      <c r="M10" t="s">
+        <v>48</v>
+      </c>
+      <c r="N10">
+        <v>328090</v>
+      </c>
+      <c r="O10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" t="s">
         <v>37</v>
       </c>
-      <c r="F4">
-        <v>37.68</v>
-      </c>
-      <c r="G4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4">
-        <v>1.45</v>
-      </c>
-      <c r="I4" s="1">
-        <v>54.64</v>
-      </c>
-      <c r="J4">
-        <v>1.52</v>
-      </c>
-      <c r="K4" s="1">
-        <v>57.27</v>
-      </c>
-      <c r="L4" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4">
-        <v>326980</v>
-      </c>
-      <c r="N4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="E11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11">
+        <v>54.28</v>
+      </c>
+      <c r="G11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11">
+        <v>1.564</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1.604</v>
+      </c>
+      <c r="J11">
+        <v>87.06511999999999</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="L11" s="1">
+        <v>91.1904</v>
+      </c>
+      <c r="M11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12">
+        <v>33.712</v>
+      </c>
+      <c r="G12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12">
+        <v>1.588</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1.628</v>
+      </c>
+      <c r="J12">
+        <v>54.883136</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="L12" s="1">
+        <v>57.3104</v>
+      </c>
+      <c r="M12" t="s">
+        <v>50</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
         <v>28</v>
       </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5">
-        <v>48.16</v>
-      </c>
-      <c r="G5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5">
-        <v>1.45</v>
-      </c>
-      <c r="I5" s="1">
-        <v>69.83</v>
-      </c>
-      <c r="J5">
-        <v>1.52</v>
-      </c>
-      <c r="K5" s="1">
-        <v>73.2</v>
-      </c>
-      <c r="L5" t="s">
-        <v>42</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6">
-        <v>52.6</v>
-      </c>
-      <c r="G6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6">
-        <v>1.49</v>
-      </c>
-      <c r="I6" s="1">
-        <v>78.37</v>
-      </c>
-      <c r="J6">
-        <v>1.56</v>
-      </c>
-      <c r="K6" s="1">
-        <v>82.06</v>
-      </c>
-      <c r="L6" t="s">
-        <v>43</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="C13" t="s">
         <v>31</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D13" t="s">
         <v>35</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7">
-        <v>44.83</v>
-      </c>
-      <c r="G7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7">
-        <v>1.49</v>
-      </c>
-      <c r="I7" s="1">
-        <v>66.8</v>
-      </c>
-      <c r="J7">
-        <v>1.56</v>
-      </c>
-      <c r="K7" s="1">
-        <v>69.930000000000007</v>
-      </c>
-      <c r="L7" t="s">
-        <v>44</v>
-      </c>
-      <c r="M7">
-        <v>434962</v>
-      </c>
-      <c r="N7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="E13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13">
+        <v>49.269</v>
+      </c>
+      <c r="G13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13">
+        <v>1.619</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1.659</v>
+      </c>
+      <c r="J13">
+        <v>81.73727100000001</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="L13" s="1">
+        <v>86.22075</v>
+      </c>
+      <c r="M13" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13">
+        <v>328540</v>
+      </c>
+      <c r="O13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
         <v>27</v>
       </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8">
-        <v>51.61</v>
-      </c>
-      <c r="G8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8">
-        <v>1.49</v>
-      </c>
-      <c r="I8" s="1">
-        <v>76.900000000000006</v>
-      </c>
-      <c r="J8">
-        <v>1.56</v>
-      </c>
-      <c r="K8" s="1">
-        <v>80.510000000000005</v>
-      </c>
-      <c r="L8" t="s">
-        <v>45</v>
-      </c>
-      <c r="M8">
-        <v>327450</v>
-      </c>
-      <c r="N8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9">
-        <v>25.35</v>
-      </c>
-      <c r="G9" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9">
-        <v>1.53</v>
-      </c>
-      <c r="I9" s="1">
-        <v>38.79</v>
-      </c>
-      <c r="J9">
-        <v>1.58</v>
-      </c>
-      <c r="K9" s="1">
-        <v>40.049999999999997</v>
-      </c>
-      <c r="L9" t="s">
-        <v>46</v>
-      </c>
-      <c r="M9">
-        <v>327760</v>
-      </c>
-      <c r="N9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10">
-        <v>42.92</v>
-      </c>
-      <c r="G10" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10">
-        <v>1.59</v>
-      </c>
-      <c r="I10" s="1">
-        <v>68.239999999999995</v>
-      </c>
-      <c r="J10">
-        <v>1.68</v>
-      </c>
-      <c r="K10" s="1">
-        <v>72.11</v>
-      </c>
-      <c r="L10" t="s">
-        <v>47</v>
-      </c>
-      <c r="M10">
-        <v>328090</v>
-      </c>
-      <c r="N10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="10" t="s">
+      <c r="C14" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D14" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="10">
-        <v>54.28</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" s="10">
-        <v>1.6</v>
-      </c>
-      <c r="I11" s="11">
-        <v>86.85</v>
-      </c>
-      <c r="J11" s="10">
-        <v>1.68</v>
-      </c>
-      <c r="K11" s="11">
-        <v>91.19</v>
-      </c>
-      <c r="L11" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11" s="10">
-        <v>0</v>
-      </c>
-      <c r="N11" s="10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12">
-        <v>33.71</v>
-      </c>
-      <c r="G12" t="s">
-        <v>38</v>
-      </c>
-      <c r="H12">
-        <v>1.63</v>
-      </c>
-      <c r="I12" s="1">
-        <v>54.95</v>
-      </c>
-      <c r="J12">
-        <v>1.7</v>
-      </c>
-      <c r="K12" s="1">
-        <v>57.31</v>
-      </c>
-      <c r="L12" t="s">
-        <v>49</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13">
-        <v>49.27</v>
-      </c>
-      <c r="G13" t="s">
-        <v>38</v>
-      </c>
-      <c r="H13">
-        <v>1.66</v>
-      </c>
-      <c r="I13" s="1">
-        <v>81.790000000000006</v>
-      </c>
-      <c r="J13">
-        <v>1.75</v>
-      </c>
-      <c r="K13" s="1">
-        <v>86.22</v>
-      </c>
-      <c r="L13" t="s">
-        <v>50</v>
-      </c>
-      <c r="M13">
-        <v>328540</v>
-      </c>
-      <c r="N13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" t="s">
-        <v>35</v>
-      </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F14">
         <v>47.76</v>
       </c>
       <c r="G14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H14">
-        <v>1.69</v>
+        <v>1.653</v>
       </c>
       <c r="I14" s="1">
-        <v>80.709999999999994</v>
+        <v>1.693</v>
       </c>
       <c r="J14">
+        <v>80.85768</v>
+      </c>
+      <c r="K14" s="1">
         <v>1.75</v>
       </c>
-      <c r="K14" s="1">
+      <c r="L14" s="1">
         <v>83.58</v>
       </c>
-      <c r="L14" t="s">
-        <v>51</v>
-      </c>
-      <c r="M14">
+      <c r="M14" t="s">
+        <v>52</v>
+      </c>
+      <c r="N14">
         <v>435629</v>
       </c>
-      <c r="N14" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15">
+        <v>54.731</v>
+      </c>
+      <c r="G15" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15">
+        <v>1.674</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1.714</v>
+      </c>
+      <c r="J15">
+        <v>93.80893399999999</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="L15" s="1">
+        <v>95.77925</v>
+      </c>
+      <c r="M15" t="s">
+        <v>50</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" t="s">
         <v>26</v>
       </c>
-      <c r="C15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" t="s">
-        <v>37</v>
-      </c>
-      <c r="F15">
-        <v>54.73</v>
-      </c>
-      <c r="G15" t="s">
-        <v>38</v>
-      </c>
-      <c r="H15">
-        <v>1.71</v>
-      </c>
-      <c r="I15" s="1">
-        <v>93.59</v>
-      </c>
-      <c r="J15">
-        <v>1.75</v>
-      </c>
-      <c r="K15" s="1">
-        <v>95.78</v>
-      </c>
-      <c r="L15" t="s">
-        <v>49</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>25</v>
-      </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F16">
-        <v>34.1</v>
+        <v>34.102</v>
       </c>
       <c r="G16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H16">
-        <v>1.71</v>
+        <v>1.674</v>
       </c>
       <c r="I16" s="1">
-        <v>58.31</v>
+        <v>1.714</v>
       </c>
       <c r="J16">
+        <v>58.450828</v>
+      </c>
+      <c r="K16" s="1">
         <v>1.76</v>
       </c>
-      <c r="K16" s="1">
-        <v>60.02</v>
-      </c>
-      <c r="L16" t="s">
-        <v>52</v>
-      </c>
-      <c r="M16">
+      <c r="L16" s="1">
+        <v>60.01952</v>
+      </c>
+      <c r="M16" t="s">
+        <v>53</v>
+      </c>
+      <c r="N16">
         <v>328945</v>
       </c>
-      <c r="N16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
+      <c r="O16" t="s">
         <v>68</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="5">
-        <v>657.5</v>
-      </c>
-      <c r="C21" s="5">
+      <c r="D20" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="6">
+        <v>657.503</v>
+      </c>
+      <c r="C21" s="6">
         <v>15</v>
       </c>
-      <c r="D21" s="6">
-        <v>1.559985</v>
-      </c>
-      <c r="E21" s="5">
-        <v>1025.69</v>
-      </c>
-      <c r="F21" s="5">
+      <c r="D21" s="7">
+        <v>1.560169</v>
+      </c>
+      <c r="E21" s="6">
+        <v>1025.82</v>
+      </c>
+      <c r="F21" s="6">
         <v>1070.79</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" s="8">
-        <v>657.5</v>
-      </c>
-      <c r="C22" s="8">
+    <row r="22" spans="1:6">
+      <c r="A22" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="9">
+        <v>657.503</v>
+      </c>
+      <c r="C22" s="9">
         <v>15</v>
       </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="8">
-        <v>1025.69</v>
-      </c>
-      <c r="F22" s="8">
+      <c r="D22" s="7"/>
+      <c r="E22" s="9">
+        <v>1025.82</v>
+      </c>
+      <c r="F22" s="9">
         <v>1070.79</v>
       </c>
     </row>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД/ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="74">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -246,8 +243,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -340,10 +337,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -638,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -651,13 +648,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -700,718 +697,670 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2">
         <v>54.013</v>
       </c>
       <c r="G2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2">
+        <v>1.439</v>
+      </c>
+      <c r="I2" s="1">
+        <v>77.72499999999999</v>
+      </c>
+      <c r="J2">
+        <v>1.51</v>
+      </c>
+      <c r="K2" s="1">
+        <v>81.56</v>
+      </c>
+      <c r="L2" t="s">
         <v>39</v>
       </c>
-      <c r="H2">
-        <v>1.399</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.439</v>
-      </c>
-      <c r="J2">
-        <v>77.724707</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L2" s="1">
-        <v>81.55963</v>
-      </c>
-      <c r="M2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3">
         <v>26.49</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H3">
-        <v>1.399</v>
+        <v>1.439</v>
       </c>
       <c r="I3" s="1">
-        <v>1.439</v>
+        <v>38.119</v>
       </c>
       <c r="J3">
-        <v>38.11911</v>
+        <v>1.51</v>
       </c>
       <c r="K3" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L3" s="1">
-        <v>39.9999</v>
-      </c>
-      <c r="M3" t="s">
-        <v>41</v>
-      </c>
-      <c r="N3">
+        <v>40</v>
+      </c>
+      <c r="L3" t="s">
+        <v>40</v>
+      </c>
+      <c r="M3">
         <v>326780</v>
       </c>
-      <c r="O3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F4">
         <v>37.678</v>
       </c>
       <c r="G4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H4">
-        <v>1.406</v>
+        <v>1.446</v>
       </c>
       <c r="I4" s="1">
-        <v>1.446</v>
+        <v>54.482</v>
       </c>
       <c r="J4">
-        <v>54.482388</v>
+        <v>1.52</v>
       </c>
       <c r="K4" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L4" s="1">
-        <v>57.27056</v>
-      </c>
-      <c r="M4" t="s">
-        <v>42</v>
-      </c>
-      <c r="N4">
+        <v>57.271</v>
+      </c>
+      <c r="L4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4">
         <v>326980</v>
       </c>
-      <c r="O4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F5">
         <v>48.158</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H5">
-        <v>1.406</v>
+        <v>1.446</v>
       </c>
       <c r="I5" s="1">
-        <v>1.446</v>
+        <v>69.636</v>
       </c>
       <c r="J5">
-        <v>69.63646799999999</v>
+        <v>1.52</v>
       </c>
       <c r="K5" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L5" s="1">
-        <v>73.20016</v>
-      </c>
-      <c r="M5" t="s">
-        <v>43</v>
-      </c>
-      <c r="N5">
+        <v>73.2</v>
+      </c>
+      <c r="L5" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F6">
         <v>52.603</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H6">
-        <v>1.451</v>
+        <v>1.491</v>
       </c>
       <c r="I6" s="1">
-        <v>1.491</v>
+        <v>78.431</v>
       </c>
       <c r="J6">
-        <v>78.431073</v>
+        <v>1.56</v>
       </c>
       <c r="K6" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L6" s="1">
-        <v>82.06068</v>
-      </c>
-      <c r="M6" t="s">
-        <v>44</v>
-      </c>
-      <c r="N6">
+        <v>82.06100000000001</v>
+      </c>
+      <c r="L6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="O6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7">
         <v>44.827</v>
       </c>
       <c r="G7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H7">
-        <v>1.451</v>
+        <v>1.491</v>
       </c>
       <c r="I7" s="1">
-        <v>1.491</v>
+        <v>66.837</v>
       </c>
       <c r="J7">
-        <v>66.837057</v>
+        <v>1.56</v>
       </c>
       <c r="K7" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L7" s="1">
-        <v>69.93012</v>
-      </c>
-      <c r="M7" t="s">
-        <v>45</v>
-      </c>
-      <c r="N7">
+        <v>69.93000000000001</v>
+      </c>
+      <c r="L7" t="s">
+        <v>44</v>
+      </c>
+      <c r="M7">
         <v>434962</v>
       </c>
-      <c r="O7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F8">
         <v>51.609</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H8">
-        <v>1.451</v>
+        <v>1.491</v>
       </c>
       <c r="I8" s="1">
-        <v>1.491</v>
+        <v>76.949</v>
       </c>
       <c r="J8">
-        <v>76.94901900000001</v>
+        <v>1.56</v>
       </c>
       <c r="K8" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L8" s="1">
-        <v>80.51004</v>
-      </c>
-      <c r="M8" t="s">
-        <v>46</v>
-      </c>
-      <c r="N8">
+        <v>80.51000000000001</v>
+      </c>
+      <c r="L8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M8">
         <v>327450</v>
       </c>
-      <c r="O8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F9">
         <v>25.348</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H9">
-        <v>1.489</v>
+        <v>1.529</v>
       </c>
       <c r="I9" s="1">
-        <v>1.529</v>
+        <v>38.757</v>
       </c>
       <c r="J9">
-        <v>38.757092</v>
+        <v>1.58</v>
       </c>
       <c r="K9" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="L9" s="1">
-        <v>40.04984</v>
-      </c>
-      <c r="M9" t="s">
-        <v>47</v>
-      </c>
-      <c r="N9">
+        <v>40.05</v>
+      </c>
+      <c r="L9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M9">
         <v>327760</v>
       </c>
-      <c r="O9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F10">
         <v>42.923</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H10">
-        <v>1.546</v>
+        <v>1.586</v>
       </c>
       <c r="I10" s="1">
-        <v>1.586</v>
+        <v>68.07599999999999</v>
       </c>
       <c r="J10">
-        <v>68.075878</v>
+        <v>1.68</v>
       </c>
       <c r="K10" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L10" s="1">
-        <v>72.11064</v>
-      </c>
-      <c r="M10" t="s">
-        <v>48</v>
-      </c>
-      <c r="N10">
+        <v>72.111</v>
+      </c>
+      <c r="L10" t="s">
+        <v>47</v>
+      </c>
+      <c r="M10">
         <v>328090</v>
       </c>
-      <c r="O10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="N10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F11">
         <v>54.28</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H11">
-        <v>1.564</v>
+        <v>1.604</v>
       </c>
       <c r="I11" s="1">
-        <v>1.604</v>
+        <v>87.065</v>
       </c>
       <c r="J11">
-        <v>87.06511999999999</v>
+        <v>1.68</v>
       </c>
       <c r="K11" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L11" s="1">
-        <v>91.1904</v>
-      </c>
-      <c r="M11" t="s">
-        <v>49</v>
-      </c>
-      <c r="N11">
+        <v>91.19</v>
+      </c>
+      <c r="L11" t="s">
+        <v>48</v>
+      </c>
+      <c r="M11">
         <v>0</v>
       </c>
-      <c r="O11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="N11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F12">
         <v>33.712</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H12">
-        <v>1.588</v>
+        <v>1.628</v>
       </c>
       <c r="I12" s="1">
-        <v>1.628</v>
+        <v>54.883</v>
       </c>
       <c r="J12">
-        <v>54.883136</v>
+        <v>1.7</v>
       </c>
       <c r="K12" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L12" s="1">
-        <v>57.3104</v>
-      </c>
-      <c r="M12" t="s">
-        <v>50</v>
-      </c>
-      <c r="N12">
+        <v>57.31</v>
+      </c>
+      <c r="L12" t="s">
+        <v>49</v>
+      </c>
+      <c r="M12">
         <v>0</v>
       </c>
-      <c r="O12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="N12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F13">
         <v>49.269</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H13">
-        <v>1.619</v>
+        <v>1.659</v>
       </c>
       <c r="I13" s="1">
-        <v>1.659</v>
+        <v>81.73699999999999</v>
       </c>
       <c r="J13">
-        <v>81.73727100000001</v>
+        <v>1.75</v>
       </c>
       <c r="K13" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L13" s="1">
-        <v>86.22075</v>
-      </c>
-      <c r="M13" t="s">
-        <v>51</v>
-      </c>
-      <c r="N13">
+        <v>86.221</v>
+      </c>
+      <c r="L13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13">
         <v>328540</v>
       </c>
-      <c r="O13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="N13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F14">
         <v>47.76</v>
       </c>
       <c r="G14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H14">
-        <v>1.653</v>
+        <v>1.693</v>
       </c>
       <c r="I14" s="1">
-        <v>1.693</v>
+        <v>80.858</v>
       </c>
       <c r="J14">
-        <v>80.85768</v>
+        <v>1.75</v>
       </c>
       <c r="K14" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L14" s="1">
         <v>83.58</v>
       </c>
-      <c r="M14" t="s">
-        <v>52</v>
-      </c>
-      <c r="N14">
+      <c r="L14" t="s">
+        <v>51</v>
+      </c>
+      <c r="M14">
         <v>435629</v>
       </c>
-      <c r="O14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="N14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F15">
         <v>54.731</v>
       </c>
       <c r="G15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H15">
-        <v>1.674</v>
+        <v>1.714</v>
       </c>
       <c r="I15" s="1">
-        <v>1.714</v>
+        <v>93.809</v>
       </c>
       <c r="J15">
-        <v>93.80893399999999</v>
+        <v>1.75</v>
       </c>
       <c r="K15" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L15" s="1">
-        <v>95.77925</v>
-      </c>
-      <c r="M15" t="s">
-        <v>50</v>
-      </c>
-      <c r="N15">
+        <v>95.779</v>
+      </c>
+      <c r="L15" t="s">
+        <v>49</v>
+      </c>
+      <c r="M15">
         <v>0</v>
       </c>
-      <c r="O15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="N15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F16">
         <v>34.102</v>
       </c>
       <c r="G16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H16">
-        <v>1.674</v>
+        <v>1.714</v>
       </c>
       <c r="I16" s="1">
-        <v>1.714</v>
+        <v>58.451</v>
       </c>
       <c r="J16">
-        <v>58.450828</v>
+        <v>1.76</v>
       </c>
       <c r="K16" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L16" s="1">
-        <v>60.01952</v>
-      </c>
-      <c r="M16" t="s">
-        <v>53</v>
-      </c>
-      <c r="N16">
+        <v>60.02</v>
+      </c>
+      <c r="L16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M16">
         <v>328945</v>
       </c>
-      <c r="O16" t="s">
-        <v>68</v>
+      <c r="N16" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -1421,47 +1370,47 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="C20" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="D20" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>73</v>
-      </c>
       <c r="E20" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B21" s="6">
         <v>657.503</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="7">
         <v>15</v>
       </c>
       <c r="D21" s="7">
-        <v>1.560169</v>
-      </c>
-      <c r="E21" s="6">
-        <v>1025.82</v>
-      </c>
-      <c r="F21" s="6">
-        <v>1070.79</v>
+        <v>1.56</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1025.815</v>
+      </c>
+      <c r="F21" s="7">
+        <v>1070.793</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B22" s="9">
         <v>657.503</v>
@@ -1471,10 +1420,10 @@
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="9">
-        <v>1025.82</v>
+        <v>1025.815</v>
       </c>
       <c r="F22" s="9">
-        <v>1070.79</v>
+        <v>1070.793</v>
       </c>
     </row>
   </sheetData>
